--- a/vaibhav excelsheet.xlsx
+++ b/vaibhav excelsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585a7b6ea7d5f67/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F847EDE-C5C6-41E1-A8DB-4C7626B621B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{6F847EDE-C5C6-41E1-A8DB-4C7626B621B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F676720-60D0-4151-949C-A0B0888B0410}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -211,6 +211,12 @@
   </si>
   <si>
     <t>not felt a tiredness</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>feeling a little bit tired.</t>
   </si>
 </sst>
 </file>
@@ -1084,26 +1090,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>150</v>
+      </c>
+      <c r="E8" s="14">
+        <v>60</v>
+      </c>
+      <c r="F8" s="14">
+        <v>400</v>
+      </c>
+      <c r="G8" s="14">
+        <v>8</v>
+      </c>
+      <c r="H8" s="14">
+        <v>20</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/vaibhav excelsheet.xlsx
+++ b/vaibhav excelsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585a7b6ea7d5f67/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{6F847EDE-C5C6-41E1-A8DB-4C7626B621B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F676720-60D0-4151-949C-A0B0888B0410}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{6F847EDE-C5C6-41E1-A8DB-4C7626B621B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84842606-757D-49E8-A6A7-251156C5D588}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -210,13 +210,16 @@
     <t>August</t>
   </si>
   <si>
-    <t>not felt a tiredness</t>
+    <t>Low</t>
   </si>
   <si>
-    <t>Neutral</t>
+    <t xml:space="preserve">felt tired </t>
   </si>
   <si>
-    <t>feeling a little bit tired.</t>
+    <t>High</t>
+  </si>
+  <si>
+    <t>feeling good and happy.</t>
   </si>
 </sst>
 </file>
@@ -497,6 +500,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1045,13 +1052,13 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B7" s="14">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="C7" s="14">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D7" s="14">
         <v>120</v>
@@ -1060,21 +1067,21 @@
         <v>60</v>
       </c>
       <c r="F7" s="14">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="G7" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H7" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>975</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>550</v>
+        <v>465</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>49</v>
@@ -1083,18 +1090,18 @@
         <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B8" s="14">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C8" s="14">
         <v>30</v>
@@ -1103,36 +1110,36 @@
         <v>150</v>
       </c>
       <c r="E8" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F8" s="14">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="G8" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H8" s="14">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>910</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>530</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
